--- a/问题3/结果/表5.xlsx
+++ b/问题3/结果/表5.xlsx
@@ -456,19 +456,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1.0186</v>
+        <v>1.0188</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.9897</v>
+        <v>0.9899</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.903</v>
+        <v>0.9031</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>0.7563</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="3">
@@ -476,19 +476,19 @@
         <v>12</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.4571</v>
+        <v>0.4573</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.4441</v>
+        <v>0.4443</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.4039</v>
+        <v>0.4041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.3304</v>
+        <v>0.3305</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.1648</v>
+        <v>0.1647</v>
       </c>
     </row>
     <row r="4">
@@ -496,19 +496,19 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.2993</v>
+        <v>0.2994</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.292</v>
+        <v>0.2921</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.2691</v>
+        <v>0.2692</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.2256</v>
+        <v>0.2257</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -516,19 +516,19 @@
         <v>24</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.2381</v>
+        <v>0.2382</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.233</v>
+        <v>0.2331</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.217</v>
+        <v>0.2171</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0.1858</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.0665</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="6">
@@ -536,19 +536,19 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.206</v>
+        <v>0.2061</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.202</v>
+        <v>0.2021</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.1893</v>
+        <v>0.1894</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0.1643</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0599</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="7">
@@ -556,19 +556,19 @@
         <v>36</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.186</v>
+        <v>0.1861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.1827</v>
+        <v>0.1828</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0.172</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.1505</v>
+        <v>0.1506</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0567</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="8">
@@ -576,19 +576,19 @@
         <v>42</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.1722</v>
+        <v>0.1723</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.1693</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.1598</v>
+        <v>0.1599</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.1409</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
     </row>
     <row r="9">
@@ -596,19 +596,19 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.1619</v>
+        <v>0.162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.1593</v>
+        <v>0.1594</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.1508</v>
+        <v>0.1509</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.1336</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0537</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="10">
@@ -625,15 +625,15 @@
         <v>0.1438</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.1278</v>
+        <v>0.1279</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.053</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57.57</v>
+        <v>57.62</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.15</v>
@@ -648,7 +648,7 @@
         <v>0.125</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0527</v>
+        <v>0.0526</v>
       </c>
     </row>
   </sheetData>
